--- a/tableForISI2.xlsx
+++ b/tableForISI2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\3.ZS\Inteligentné systémy v informatike\isi-zadanie-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC617697-FD67-4C97-B4B8-1C5EBAE44D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F9CC6E-EE23-49AC-BE83-7CD2EC4D1300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
   <si>
     <t>DFS</t>
   </si>
@@ -98,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,6 +417,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F82FD1-B348-4AF1-99C8-041679FD79DD}">
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -468,46 +473,46 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>367</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>85</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>85</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.49402999877929599</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>85</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>16</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>10</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>8.7799787521362305E-2</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>659</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>202</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>10</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>1.2616610527038501</v>
       </c>
     </row>
@@ -515,46 +520,46 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>11731</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>2017</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1982</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>8.3399546146392805</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>2887</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>5141</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>41</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>101.123247861862</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>3056</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>6783</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>41</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>123.391093492507</v>
       </c>
     </row>
@@ -562,46 +567,46 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>3678</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>879</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>781</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>3.8524541854858398</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>117</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>174</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>40</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.36829853057861</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>1202</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>952</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>34</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>8.7941470146179199</v>
       </c>
     </row>
@@ -609,46 +614,46 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>29267</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>5065</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>4942</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>26.499254226684499</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>2954</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>4642</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>73</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>84.309695959091101</v>
       </c>
       <c r="K5">
         <v>4</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>4332</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>8020</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>73</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>161.36070799827499</v>
       </c>
     </row>
@@ -656,46 +661,46 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>6869</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>2081</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>1522</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>11.6879527568817</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>1274</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2001</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>84</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>22.249919891357401</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1702</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>2896</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>84</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>34.642625808715799</v>
       </c>
     </row>
@@ -703,46 +708,46 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>3166</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>673</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>663</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>2.17880082130432</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>537</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>142</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>14</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.85775279998779297</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>2923</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>1415</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>14</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>13.100692272186199</v>
       </c>
     </row>
@@ -750,46 +755,46 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>6898</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1058</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>1041</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>3.8795859813690101</v>
       </c>
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>83</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>14</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>10</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>3.5619020462036098E-2</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>2701</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>653</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>10</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>4.5208792686462402</v>
       </c>
     </row>
@@ -797,46 +802,46 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>100998</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>13155</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>12973</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>110.984115600585</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>1417</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>201</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>15</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>1.0050349235534599</v>
       </c>
       <c r="K9">
         <v>8</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>24683</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>9481</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>15</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>245.946476221084</v>
       </c>
     </row>
@@ -844,46 +849,46 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>7513</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1656</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>1588</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>6.27137947082519</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>1191</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>890</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>23</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>7.8471658229827801</v>
       </c>
       <c r="K10">
         <v>9</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>5441</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>5381</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>23</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>82.808805704116807</v>
       </c>
     </row>
@@ -891,46 +896,46 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>27422</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>4422</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>4307</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>22.659047126770002</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>396</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>105</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>14</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.55657076835632302</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>10238</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>3386</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>12</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>43.285982131958001</v>
       </c>
     </row>
@@ -938,46 +943,46 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>5305</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1191</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>15.682337045669501</v>
       </c>
       <c r="F12">
         <v>11</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>940</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1191</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>15.570354700088499</v>
       </c>
       <c r="K12">
         <v>11</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>1447</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>1191</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>13.930059432983301</v>
       </c>
       <c r="P12" t="s">
@@ -985,306 +990,316 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B14">
+      <c r="B14" s="1">
         <f>AVERAGE(B2:B11)</f>
         <v>19790.900000000001</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <f>AVERAGE(C2:C11)</f>
         <v>3109.1</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
         <v>2988.4</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <f>AVERAGE(E2:E11)</f>
         <v>19.684657478332415</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <f>AVERAGE(G2:G11)</f>
         <v>1094.0999999999999</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <f>AVERAGE(H2:H11)</f>
         <v>1332.6</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <f>AVERAGE(I2:I11)</f>
         <v>32.4</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <f>AVERAGE(J2:J11)</f>
         <v>21.944110536575288</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <f>AVERAGE(L2:L11)</f>
         <v>5693.7</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <f>AVERAGE(M2:M11)</f>
         <v>3916.9</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <f>AVERAGE(N2:N11)</f>
         <v>31.6</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <f>AVERAGE(O2:O11)</f>
         <v>71.911307096481082</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B15">
+      <c r="B15" s="1">
         <f>AVERAGE(B2:B12)</f>
         <v>18474</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
         <v>2934.7272727272725</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <f>AVERAGE(D2:D12)</f>
         <v>2988.4</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <f>AVERAGE(E2:E12)</f>
         <v>19.32081016627215</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <f>AVERAGE(G2:G12)</f>
         <v>1080.090909090909</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <f>AVERAGE(H2:H12)</f>
         <v>1319.7272727272727</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <f>AVERAGE(I2:I12)</f>
         <v>32.4</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <f>AVERAGE(J2:J12)</f>
         <v>21.364678187803761</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <f>AVERAGE(L2:L12)</f>
         <v>5307.636363636364</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <f>AVERAGE(M2:M12)</f>
         <v>3669.090909090909</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <f>AVERAGE(N2:N12)</f>
         <v>31.6</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <f>AVERAGE(O2:O12)</f>
         <v>66.640284581617649</v>
       </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>MAX(B5:B14)</f>
+      <c r="P15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <f>MAX(B2:B11)</f>
         <v>100998</v>
       </c>
-      <c r="C17">
-        <f t="shared" ref="C17:O17" si="0">MAX(C5:C14)</f>
+      <c r="C17" s="1">
+        <f t="shared" ref="C17:O17" si="0">MAX(C2:C11)</f>
         <v>13155</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <f t="shared" si="0"/>
         <v>12973</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <f t="shared" si="0"/>
         <v>110.984115600585</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <f t="shared" si="0"/>
         <v>2954</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <f t="shared" si="0"/>
-        <v>4642</v>
-      </c>
-      <c r="I17">
+        <v>5141</v>
+      </c>
+      <c r="I17" s="1">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <f t="shared" si="0"/>
-        <v>84.309695959091101</v>
-      </c>
-      <c r="L17">
+        <v>101.123247861862</v>
+      </c>
+      <c r="L17" s="1">
         <f t="shared" si="0"/>
         <v>24683</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <f t="shared" si="0"/>
         <v>9481</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <f t="shared" si="0"/>
         <v>245.946476221084</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
         <f>MAX(B2:B12)</f>
         <v>100998</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <f t="shared" ref="C18:O18" si="1">MAX(C2:C12)</f>
         <v>13155</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <f t="shared" si="1"/>
         <v>12973</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>110.984115600585</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <f t="shared" si="1"/>
         <v>2954</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>5141</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <f t="shared" si="1"/>
         <v>101.123247861862</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <f t="shared" si="1"/>
         <v>24683</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <f t="shared" si="1"/>
         <v>9481</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <f t="shared" si="1"/>
         <v>245.946476221084</v>
       </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <f>MIN(B5:B14)</f>
-        <v>3166</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ref="C20:O20" si="2">MIN(C5:C14)</f>
-        <v>673</v>
-      </c>
-      <c r="D20">
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <f>MIN(B2:B11)</f>
+        <v>367</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" ref="C20:O20" si="2">MIN(C2:C11)</f>
+        <v>85</v>
+      </c>
+      <c r="D20" s="1">
         <f t="shared" si="2"/>
-        <v>663</v>
-      </c>
-      <c r="E20">
+        <v>85</v>
+      </c>
+      <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>2.17880082130432</v>
-      </c>
-      <c r="G20">
+        <v>0.49402999877929599</v>
+      </c>
+      <c r="G20" s="1">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <f t="shared" si="2"/>
         <v>3.5619020462036098E-2</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <f t="shared" si="2"/>
-        <v>1447</v>
-      </c>
-      <c r="M20">
+        <v>659</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="2"/>
-        <v>653</v>
-      </c>
-      <c r="N20">
+        <v>202</v>
+      </c>
+      <c r="N20" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <f t="shared" si="2"/>
-        <v>4.5208792686462402</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21">
+        <v>1.2616610527038501</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
         <f>MIN(B2:B12)</f>
         <v>367</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <f t="shared" ref="C21:O21" si="3">MIN(C2:C12)</f>
         <v>85</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <f t="shared" si="3"/>
         <v>0.49402999877929599</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <f t="shared" si="3"/>
         <v>83</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <f t="shared" si="3"/>
         <v>3.5619020462036098E-2</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <f t="shared" si="3"/>
         <v>659</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <f t="shared" si="3"/>
         <v>1.2616610527038501</v>
       </c>
+      <c r="P21" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tableForISI2.xlsx
+++ b/tableForISI2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\3.ZS\Inteligentné systémy v informatike\isi-zadanie-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F9CC6E-EE23-49AC-BE83-7CD2EC4D1300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF191C7-147B-4168-8342-95661378CF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
+    <workbookView xWindow="28830" yWindow="15" windowWidth="20370" windowHeight="10770" activeTab="1" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="9">
   <si>
     <t>DFS</t>
   </si>
@@ -1302,4 +1303,890 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B70EE66-2D12-46E9-875E-D03ADF893730}">
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>741</v>
+      </c>
+      <c r="C2" s="1">
+        <v>318</v>
+      </c>
+      <c r="D2" s="1">
+        <v>302</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.99832963943481</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>60</v>
+      </c>
+      <c r="H2" s="1">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>9.2631340026855399E-2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>145</v>
+      </c>
+      <c r="M2" s="1">
+        <v>203</v>
+      </c>
+      <c r="N2" s="1">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.96251773834228505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3239</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3263</v>
+      </c>
+      <c r="D3" s="1">
+        <v>952</v>
+      </c>
+      <c r="E3" s="1">
+        <v>33.768999576568604</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1658</v>
+      </c>
+      <c r="H3" s="1">
+        <v>5130</v>
+      </c>
+      <c r="I3" s="1">
+        <v>41</v>
+      </c>
+      <c r="J3" s="1">
+        <v>54.0281014442443</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" s="1">
+        <v>573</v>
+      </c>
+      <c r="M3" s="1">
+        <v>6784</v>
+      </c>
+      <c r="N3" s="1">
+        <v>41</v>
+      </c>
+      <c r="O3" s="1">
+        <v>68.475329399108801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>650</v>
+      </c>
+      <c r="C4" s="1">
+        <v>300</v>
+      </c>
+      <c r="D4" s="1">
+        <v>281</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.5600559711456199</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>78</v>
+      </c>
+      <c r="H4" s="1">
+        <v>174</v>
+      </c>
+      <c r="I4" s="1">
+        <v>40</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.83087229728698697</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1">
+        <v>165</v>
+      </c>
+      <c r="M4" s="1">
+        <v>953</v>
+      </c>
+      <c r="N4" s="1">
+        <v>34</v>
+      </c>
+      <c r="O4" s="1">
+        <v>5.4922838211059499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3923</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1556</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1392</v>
+      </c>
+      <c r="E5" s="1">
+        <v>14.670815706253</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1616</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4643</v>
+      </c>
+      <c r="I5" s="1">
+        <v>73</v>
+      </c>
+      <c r="J5" s="1">
+        <v>43.755789279937702</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5" s="1">
+        <v>625</v>
+      </c>
+      <c r="M5" s="1">
+        <v>8021</v>
+      </c>
+      <c r="N5" s="1">
+        <v>73</v>
+      </c>
+      <c r="O5" s="1">
+        <v>85.455241441726599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1671</v>
+      </c>
+      <c r="C6" s="1">
+        <v>917</v>
+      </c>
+      <c r="D6" s="1">
+        <v>789</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.2309331893920898</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>331</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2002</v>
+      </c>
+      <c r="I6" s="1">
+        <v>84</v>
+      </c>
+      <c r="J6" s="1">
+        <v>15.3655049800872</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6" s="1">
+        <v>249</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2897</v>
+      </c>
+      <c r="N6" s="1">
+        <v>84</v>
+      </c>
+      <c r="O6" s="1">
+        <v>22.541660308837798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>180</v>
+      </c>
+      <c r="C7" s="1">
+        <v>91</v>
+      </c>
+      <c r="D7" s="1">
+        <v>75</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.498364448547363</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>201</v>
+      </c>
+      <c r="H7" s="1">
+        <v>143</v>
+      </c>
+      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.955000400543212</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7" s="1">
+        <v>521</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1416</v>
+      </c>
+      <c r="N7" s="1">
+        <v>14</v>
+      </c>
+      <c r="O7" s="1">
+        <v>9.6089999675750697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>225</v>
+      </c>
+      <c r="C8" s="1">
+        <v>58</v>
+      </c>
+      <c r="D8" s="1">
+        <v>57</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.28563117980956998</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" s="1">
+        <v>66</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7.8276395797729395E-2</v>
+      </c>
+      <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8" s="1">
+        <v>517</v>
+      </c>
+      <c r="M8" s="1">
+        <v>654</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10</v>
+      </c>
+      <c r="O8" s="1">
+        <v>3.9081401824951101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6709</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1638</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1621</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24.309610605239801</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <v>535</v>
+      </c>
+      <c r="H9" s="1">
+        <v>202</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.3985838890075599</v>
+      </c>
+      <c r="K9">
+        <v>8</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2662</v>
+      </c>
+      <c r="M9" s="1">
+        <v>9482</v>
+      </c>
+      <c r="N9" s="1">
+        <v>15</v>
+      </c>
+      <c r="O9" s="1">
+        <v>198.20635867118801</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2253</v>
+      </c>
+      <c r="C10" s="1">
+        <v>865</v>
+      </c>
+      <c r="D10" s="1">
+        <v>825</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5.5225529670715297</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1">
+        <v>684</v>
+      </c>
+      <c r="H10" s="1">
+        <v>838</v>
+      </c>
+      <c r="I10" s="1">
+        <v>23</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4.5817315578460596</v>
+      </c>
+      <c r="K10">
+        <v>9</v>
+      </c>
+      <c r="L10" s="1">
+        <v>996</v>
+      </c>
+      <c r="M10" s="1">
+        <v>5382</v>
+      </c>
+      <c r="N10" s="1">
+        <v>23</v>
+      </c>
+      <c r="O10" s="1">
+        <v>50.296620607376099</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2276</v>
+      </c>
+      <c r="C11" s="1">
+        <v>809</v>
+      </c>
+      <c r="D11" s="1">
+        <v>749</v>
+      </c>
+      <c r="E11" s="1">
+        <v>6.00392270088195</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1">
+        <v>201</v>
+      </c>
+      <c r="H11" s="1">
+        <v>106</v>
+      </c>
+      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.70326399803161599</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1774</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3387</v>
+      </c>
+      <c r="N11" s="1">
+        <v>12</v>
+      </c>
+      <c r="O11" s="1">
+        <v>32.741742610931396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>694</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1191</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8.09883213043212</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1">
+        <v>370</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1191</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7.8146562576293901</v>
+      </c>
+      <c r="K12">
+        <v>11</v>
+      </c>
+      <c r="L12" s="1">
+        <v>278</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1191</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="1">
+        <v>7.5802760124206499</v>
+      </c>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <f>AVERAGE(B2:B11)</f>
+        <v>2186.6999999999998</v>
+      </c>
+      <c r="C14" s="1">
+        <f>AVERAGE(C2:C11)</f>
+        <v>981.5</v>
+      </c>
+      <c r="D14" s="1">
+        <f>AVERAGE(D2:D11)</f>
+        <v>704.3</v>
+      </c>
+      <c r="E14" s="1">
+        <f>AVERAGE(E2:E11)</f>
+        <v>9.584921598434434</v>
+      </c>
+      <c r="G14" s="1">
+        <f>AVERAGE(G2:G11)</f>
+        <v>543</v>
+      </c>
+      <c r="H14" s="1">
+        <f>AVERAGE(H2:H11)</f>
+        <v>1327</v>
+      </c>
+      <c r="I14" s="1">
+        <f>AVERAGE(I2:I11)</f>
+        <v>32.4</v>
+      </c>
+      <c r="J14" s="1">
+        <f>AVERAGE(J2:J11)</f>
+        <v>12.178975558280921</v>
+      </c>
+      <c r="L14" s="1">
+        <f>AVERAGE(L2:L11)</f>
+        <v>822.7</v>
+      </c>
+      <c r="M14" s="1">
+        <f>AVERAGE(M2:M11)</f>
+        <v>3917.9</v>
+      </c>
+      <c r="N14" s="1">
+        <f>AVERAGE(N2:N11)</f>
+        <v>31.6</v>
+      </c>
+      <c r="O14" s="1">
+        <f>AVERAGE(O2:O11)</f>
+        <v>47.768889474868715</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <f>AVERAGE(B2:B12)</f>
+        <v>2051</v>
+      </c>
+      <c r="C15" s="1">
+        <f>AVERAGE(C2:C12)</f>
+        <v>1000.5454545454545</v>
+      </c>
+      <c r="D15" s="1">
+        <f>AVERAGE(D2:D12)</f>
+        <v>704.3</v>
+      </c>
+      <c r="E15" s="1">
+        <f>AVERAGE(E2:E12)</f>
+        <v>9.449822555888769</v>
+      </c>
+      <c r="G15" s="1">
+        <f>AVERAGE(G2:G12)</f>
+        <v>527.27272727272725</v>
+      </c>
+      <c r="H15" s="1">
+        <f>AVERAGE(H2:H12)</f>
+        <v>1314.6363636363637</v>
+      </c>
+      <c r="I15" s="1">
+        <f>AVERAGE(I2:I12)</f>
+        <v>32.4</v>
+      </c>
+      <c r="J15" s="1">
+        <f>AVERAGE(J2:J12)</f>
+        <v>11.782219258221689</v>
+      </c>
+      <c r="L15" s="1">
+        <f>AVERAGE(L2:L12)</f>
+        <v>773.18181818181813</v>
+      </c>
+      <c r="M15" s="1">
+        <f>AVERAGE(M2:M12)</f>
+        <v>3670</v>
+      </c>
+      <c r="N15" s="1">
+        <f>AVERAGE(N2:N12)</f>
+        <v>31.6</v>
+      </c>
+      <c r="O15" s="1">
+        <f>AVERAGE(O2:O12)</f>
+        <v>44.115379160100709</v>
+      </c>
+      <c r="P15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <f>MAX(B2:B11)</f>
+        <v>6709</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" ref="C17:O17" si="0">MAX(C2:C11)</f>
+        <v>3263</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>1621</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>33.768999576568604</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="0"/>
+        <v>1658</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="0"/>
+        <v>5130</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="0"/>
+        <v>54.0281014442443</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="0"/>
+        <v>2662</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" si="0"/>
+        <v>9482</v>
+      </c>
+      <c r="N17" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="O17" s="1">
+        <f t="shared" si="0"/>
+        <v>198.20635867118801</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <f>MAX(B2:B12)</f>
+        <v>6709</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" ref="C18:O18" si="1">MAX(C2:C12)</f>
+        <v>3263</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="1"/>
+        <v>1621</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>33.768999576568604</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="1"/>
+        <v>1658</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>5130</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+        <v>54.0281014442443</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="1"/>
+        <v>2662</v>
+      </c>
+      <c r="M18" s="1">
+        <f t="shared" si="1"/>
+        <v>9482</v>
+      </c>
+      <c r="N18" s="1">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="O18" s="1">
+        <f t="shared" si="1"/>
+        <v>198.20635867118801</v>
+      </c>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <f>MIN(B2:B11)</f>
+        <v>180</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" ref="C20:O20" si="2">MIN(C2:C11)</f>
+        <v>58</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.28563117980956998</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="2"/>
+        <v>7.8276395797729395E-2</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="2"/>
+        <v>203</v>
+      </c>
+      <c r="N20" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="O20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.96251773834228505</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <f>MIN(B2:B12)</f>
+        <v>180</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" ref="C21:O21" si="3">MIN(C2:C12)</f>
+        <v>58</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="3"/>
+        <v>0.28563117980956998</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="3"/>
+        <v>7.8276395797729395E-2</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+      <c r="N21" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="O21" s="1">
+        <f t="shared" si="3"/>
+        <v>0.96251773834228505</v>
+      </c>
+      <c r="P21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tableForISI2.xlsx
+++ b/tableForISI2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\3.ZS\Inteligentné systémy v informatike\isi-zadanie-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF191C7-147B-4168-8342-95661378CF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12387988-6DDF-4277-BD8E-36C5A90D8432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28830" yWindow="15" windowWidth="20370" windowHeight="10770" activeTab="1" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{19922381-B718-4758-A960-AEFE3331A19D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1362,46 +1362,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>741</v>
+        <v>255</v>
       </c>
       <c r="C2" s="1">
-        <v>318</v>
+        <v>86</v>
       </c>
       <c r="D2" s="1">
-        <v>302</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1">
-        <v>1.99832963943481</v>
+        <v>0.50012660026550204</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H2" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1">
         <v>10</v>
       </c>
       <c r="J2" s="1">
-        <v>9.2631340026855399E-2</v>
+        <v>9.8672151565551702E-2</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>145</v>
+        <v>411</v>
       </c>
       <c r="M2" s="1">
-        <v>203</v>
+        <v>486</v>
       </c>
       <c r="N2" s="1">
         <v>10</v>
       </c>
       <c r="O2" s="1">
-        <v>0.96251773834228505</v>
+        <v>2.7377154827117902</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1409,46 +1409,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3239</v>
+        <v>6922</v>
       </c>
       <c r="C3" s="1">
-        <v>3263</v>
+        <v>2043</v>
       </c>
       <c r="D3" s="1">
-        <v>952</v>
+        <v>1982</v>
       </c>
       <c r="E3" s="1">
-        <v>33.768999576568604</v>
+        <v>15.4599592685699</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>1658</v>
+        <v>2383</v>
       </c>
       <c r="H3" s="1">
-        <v>5130</v>
+        <v>18498</v>
       </c>
       <c r="I3" s="1">
         <v>41</v>
       </c>
       <c r="J3" s="1">
-        <v>54.0281014442443</v>
+        <v>140.946133613586</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3" s="1">
-        <v>573</v>
+        <v>1739</v>
       </c>
       <c r="M3" s="1">
-        <v>6784</v>
+        <v>24229</v>
       </c>
       <c r="N3" s="1">
         <v>41</v>
       </c>
       <c r="O3" s="1">
-        <v>68.475329399108801</v>
+        <v>168.866213560104</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1456,46 +1456,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>650</v>
+        <v>2170</v>
       </c>
       <c r="C4" s="1">
-        <v>300</v>
+        <v>951</v>
       </c>
       <c r="D4" s="1">
-        <v>281</v>
+        <v>781</v>
       </c>
       <c r="E4" s="1">
-        <v>1.5600559711456199</v>
+        <v>4.2802038192748997</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="H4" s="1">
-        <v>174</v>
+        <v>361</v>
       </c>
       <c r="I4" s="1">
         <v>40</v>
       </c>
       <c r="J4" s="1">
-        <v>0.83087229728698697</v>
+        <v>1.4980492591857899</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
       <c r="L4" s="1">
-        <v>165</v>
+        <v>683</v>
       </c>
       <c r="M4" s="1">
-        <v>953</v>
+        <v>2703</v>
       </c>
       <c r="N4" s="1">
         <v>34</v>
       </c>
       <c r="O4" s="1">
-        <v>5.4922838211059499</v>
+        <v>11.715805292129501</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1503,46 +1503,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>3923</v>
+        <v>16945</v>
       </c>
       <c r="C5" s="1">
-        <v>1556</v>
+        <v>5126</v>
       </c>
       <c r="D5" s="1">
-        <v>1392</v>
+        <v>4942</v>
       </c>
       <c r="E5" s="1">
-        <v>14.670815706253</v>
+        <v>44.197755575179997</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>1616</v>
+        <v>2699</v>
       </c>
       <c r="H5" s="1">
-        <v>4643</v>
+        <v>16841</v>
       </c>
       <c r="I5" s="1">
         <v>73</v>
       </c>
       <c r="J5" s="1">
-        <v>43.755789279937702</v>
+        <v>115.619721889495</v>
       </c>
       <c r="K5">
         <v>4</v>
       </c>
       <c r="L5" s="1">
-        <v>625</v>
+        <v>2235</v>
       </c>
       <c r="M5" s="1">
-        <v>8021</v>
+        <v>29084</v>
       </c>
       <c r="N5" s="1">
         <v>73</v>
       </c>
       <c r="O5" s="1">
-        <v>85.455241441726599</v>
+        <v>236.39941596984801</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1550,46 +1550,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1671</v>
+        <v>4140</v>
       </c>
       <c r="C6" s="1">
-        <v>917</v>
+        <v>2831</v>
       </c>
       <c r="D6" s="1">
-        <v>789</v>
+        <v>1522</v>
       </c>
       <c r="E6" s="1">
-        <v>7.2309331893920898</v>
+        <v>18.010009765625</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>331</v>
+        <v>715</v>
       </c>
       <c r="H6" s="1">
-        <v>2002</v>
+        <v>5963</v>
       </c>
       <c r="I6" s="1">
         <v>84</v>
       </c>
       <c r="J6" s="1">
-        <v>15.3655049800872</v>
+        <v>36.711447238922098</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>249</v>
+        <v>948</v>
       </c>
       <c r="M6" s="1">
-        <v>2897</v>
+        <v>9177</v>
       </c>
       <c r="N6" s="1">
         <v>84</v>
       </c>
       <c r="O6" s="1">
-        <v>22.541660308837798</v>
+        <v>58.598631143569897</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1597,46 +1597,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>180</v>
+        <v>1990</v>
       </c>
       <c r="C7" s="1">
-        <v>91</v>
+        <v>677</v>
       </c>
       <c r="D7" s="1">
-        <v>75</v>
+        <v>663</v>
       </c>
       <c r="E7" s="1">
-        <v>0.498364448547363</v>
+        <v>3.4810545444488499</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>201</v>
+        <v>367</v>
       </c>
       <c r="H7" s="1">
-        <v>143</v>
+        <v>296</v>
       </c>
       <c r="I7" s="1">
         <v>14</v>
       </c>
       <c r="J7" s="1">
-        <v>0.955000400543212</v>
+        <v>1.4380478858947701</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>521</v>
+        <v>1647</v>
       </c>
       <c r="M7" s="1">
-        <v>1416</v>
+        <v>4248</v>
       </c>
       <c r="N7" s="1">
         <v>14</v>
       </c>
       <c r="O7" s="1">
-        <v>9.6089999675750697</v>
+        <v>23.691582202911299</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1644,22 +1644,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>225</v>
+        <v>4383</v>
       </c>
       <c r="C8" s="1">
-        <v>58</v>
+        <v>1066</v>
       </c>
       <c r="D8" s="1">
-        <v>57</v>
+        <v>1041</v>
       </c>
       <c r="E8" s="1">
-        <v>0.28563117980956998</v>
+        <v>5.2708208560943604</v>
       </c>
       <c r="F8">
         <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H8" s="1">
         <v>15</v>
@@ -1668,22 +1668,22 @@
         <v>10</v>
       </c>
       <c r="J8" s="1">
-        <v>7.8276395797729395E-2</v>
+        <v>6.7325592041015597E-2</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8" s="1">
-        <v>517</v>
+        <v>1675</v>
       </c>
       <c r="M8" s="1">
-        <v>654</v>
+        <v>1822</v>
       </c>
       <c r="N8" s="1">
         <v>10</v>
       </c>
       <c r="O8" s="1">
-        <v>3.9081401824951101</v>
+        <v>8.6603119373321498</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1691,46 +1691,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>6709</v>
+        <v>57769</v>
       </c>
       <c r="C9" s="1">
-        <v>1638</v>
+        <v>13249</v>
       </c>
       <c r="D9" s="1">
-        <v>1621</v>
+        <v>12973</v>
       </c>
       <c r="E9" s="1">
-        <v>24.309610605239801</v>
+        <v>299.941162109375</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>535</v>
+        <v>1094</v>
       </c>
       <c r="H9" s="1">
-        <v>202</v>
+        <v>431</v>
       </c>
       <c r="I9" s="1">
         <v>15</v>
       </c>
       <c r="J9" s="1">
-        <v>1.3985838890075599</v>
+        <v>2.1535272598266602</v>
       </c>
       <c r="K9">
         <v>8</v>
       </c>
       <c r="L9" s="1">
-        <v>2662</v>
+        <v>13318</v>
       </c>
       <c r="M9" s="1">
-        <v>9482</v>
+        <v>41477</v>
       </c>
       <c r="N9" s="1">
         <v>15</v>
       </c>
       <c r="O9" s="1">
-        <v>198.20635867118801</v>
+        <v>609.92586183547905</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1738,46 +1738,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2253</v>
+        <v>4301</v>
       </c>
       <c r="C10" s="1">
-        <v>865</v>
+        <v>1674</v>
       </c>
       <c r="D10" s="1">
-        <v>825</v>
+        <v>1588</v>
       </c>
       <c r="E10" s="1">
-        <v>5.5225529670715297</v>
+        <v>7.8693346977233798</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>684</v>
+        <v>927</v>
       </c>
       <c r="H10" s="1">
-        <v>838</v>
+        <v>2321</v>
       </c>
       <c r="I10" s="1">
         <v>23</v>
       </c>
       <c r="J10" s="1">
-        <v>4.5817315578460596</v>
+        <v>9.6643321514129603</v>
       </c>
       <c r="K10">
         <v>9</v>
       </c>
       <c r="L10" s="1">
-        <v>996</v>
+        <v>3066</v>
       </c>
       <c r="M10" s="1">
-        <v>5382</v>
+        <v>17387</v>
       </c>
       <c r="N10" s="1">
         <v>23</v>
       </c>
       <c r="O10" s="1">
-        <v>50.296620607376099</v>
+        <v>108.256203651428</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1785,46 +1785,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>2276</v>
+        <v>15646</v>
       </c>
       <c r="C11" s="1">
-        <v>809</v>
+        <v>4507</v>
       </c>
       <c r="D11" s="1">
-        <v>749</v>
+        <v>4307</v>
       </c>
       <c r="E11" s="1">
-        <v>6.00392270088195</v>
+        <v>35.625843763351398</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>201</v>
+        <v>294</v>
       </c>
       <c r="H11" s="1">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="I11" s="1">
         <v>14</v>
       </c>
       <c r="J11" s="1">
-        <v>0.70326399803161599</v>
+        <v>0.95225167274475098</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
       <c r="L11" s="1">
-        <v>1774</v>
+        <v>5834</v>
       </c>
       <c r="M11" s="1">
-        <v>3387</v>
+        <v>11257</v>
       </c>
       <c r="N11" s="1">
         <v>12</v>
       </c>
       <c r="O11" s="1">
-        <v>32.741742610931396</v>
+        <v>90.901697158813406</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1832,46 +1832,46 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>694</v>
+        <v>2624</v>
       </c>
       <c r="C12" s="1">
-        <v>1191</v>
+        <v>3968</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="1">
-        <v>8.09883213043212</v>
+        <v>19.5675995349884</v>
       </c>
       <c r="F12">
         <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>370</v>
+        <v>719</v>
       </c>
       <c r="H12" s="1">
-        <v>1191</v>
+        <v>3968</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J12" s="1">
-        <v>7.8146562576293901</v>
+        <v>20.551888465881301</v>
       </c>
       <c r="K12">
         <v>11</v>
       </c>
       <c r="L12" s="1">
-        <v>278</v>
+        <v>840</v>
       </c>
       <c r="M12" s="1">
-        <v>1191</v>
+        <v>3968</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O12" s="1">
-        <v>7.5802760124206499</v>
+        <v>20.312916994094799</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
@@ -1880,27 +1880,27 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <f>AVERAGE(B2:B11)</f>
-        <v>2186.6999999999998</v>
+        <v>11452.1</v>
       </c>
       <c r="C14" s="1">
         <f>AVERAGE(C2:C11)</f>
-        <v>981.5</v>
+        <v>3221</v>
       </c>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>704.3</v>
+        <v>2988.4</v>
       </c>
       <c r="E14" s="1">
         <f>AVERAGE(E2:E11)</f>
-        <v>9.584921598434434</v>
+        <v>43.463627099990831</v>
       </c>
       <c r="G14" s="1">
         <f>AVERAGE(G2:G11)</f>
-        <v>543</v>
+        <v>872.4</v>
       </c>
       <c r="H14" s="1">
         <f>AVERAGE(H2:H11)</f>
-        <v>1327</v>
+        <v>4494.7</v>
       </c>
       <c r="I14" s="1">
         <f>AVERAGE(I2:I11)</f>
@@ -1908,15 +1908,15 @@
       </c>
       <c r="J14" s="1">
         <f>AVERAGE(J2:J11)</f>
-        <v>12.178975558280921</v>
+        <v>30.914950871467465</v>
       </c>
       <c r="L14" s="1">
         <f>AVERAGE(L2:L11)</f>
-        <v>822.7</v>
+        <v>3155.6</v>
       </c>
       <c r="M14" s="1">
         <f>AVERAGE(M2:M11)</f>
-        <v>3917.9</v>
+        <v>14187</v>
       </c>
       <c r="N14" s="1">
         <f>AVERAGE(N2:N11)</f>
@@ -1924,33 +1924,33 @@
       </c>
       <c r="O14" s="1">
         <f>AVERAGE(O2:O11)</f>
-        <v>47.768889474868715</v>
+        <v>131.97534382343272</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <f>AVERAGE(B2:B12)</f>
-        <v>2051</v>
+        <v>10649.545454545454</v>
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
-        <v>1000.5454545454545</v>
+        <v>3288.909090909091</v>
       </c>
       <c r="D15" s="1">
         <f>AVERAGE(D2:D12)</f>
-        <v>704.3</v>
+        <v>2988.4</v>
       </c>
       <c r="E15" s="1">
         <f>AVERAGE(E2:E12)</f>
-        <v>9.449822555888769</v>
+        <v>41.291260957717881</v>
       </c>
       <c r="G15" s="1">
         <f>AVERAGE(G2:G12)</f>
-        <v>527.27272727272725</v>
+        <v>858.4545454545455</v>
       </c>
       <c r="H15" s="1">
         <f>AVERAGE(H2:H12)</f>
-        <v>1314.6363636363637</v>
+        <v>4446.818181818182</v>
       </c>
       <c r="I15" s="1">
         <f>AVERAGE(I2:I12)</f>
@@ -1958,15 +1958,15 @@
       </c>
       <c r="J15" s="1">
         <f>AVERAGE(J2:J12)</f>
-        <v>11.782219258221689</v>
+        <v>29.972854289141448</v>
       </c>
       <c r="L15" s="1">
         <f>AVERAGE(L2:L12)</f>
-        <v>773.18181818181813</v>
+        <v>2945.090909090909</v>
       </c>
       <c r="M15" s="1">
         <f>AVERAGE(M2:M12)</f>
-        <v>3670</v>
+        <v>13258</v>
       </c>
       <c r="N15" s="1">
         <f>AVERAGE(N2:N12)</f>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O15" s="1">
         <f>AVERAGE(O2:O12)</f>
-        <v>44.115379160100709</v>
+        <v>121.82421411167473</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
@@ -1983,27 +1983,27 @@
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <f>MAX(B2:B11)</f>
-        <v>6709</v>
+        <v>57769</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" ref="C17:O17" si="0">MAX(C2:C11)</f>
-        <v>3263</v>
+        <v>13249</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>1621</v>
+        <v>12973</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>33.768999576568604</v>
+        <v>299.941162109375</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>1658</v>
+        <v>2699</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
-        <v>5130</v>
+        <v>18498</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="0"/>
@@ -2011,15 +2011,15 @@
       </c>
       <c r="J17" s="1">
         <f t="shared" si="0"/>
-        <v>54.0281014442443</v>
+        <v>140.946133613586</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="0"/>
-        <v>2662</v>
+        <v>13318</v>
       </c>
       <c r="M17" s="1">
         <f t="shared" si="0"/>
-        <v>9482</v>
+        <v>41477</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" si="0"/>
@@ -2027,33 +2027,33 @@
       </c>
       <c r="O17" s="1">
         <f t="shared" si="0"/>
-        <v>198.20635867118801</v>
+        <v>609.92586183547905</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <f>MAX(B2:B12)</f>
-        <v>6709</v>
+        <v>57769</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" ref="C18:O18" si="1">MAX(C2:C12)</f>
-        <v>3263</v>
+        <v>13249</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="1"/>
-        <v>1621</v>
+        <v>12973</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
-        <v>33.768999576568604</v>
+        <v>299.941162109375</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="1"/>
-        <v>1658</v>
+        <v>2699</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>5130</v>
+        <v>18498</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
@@ -2061,15 +2061,15 @@
       </c>
       <c r="J18" s="1">
         <f t="shared" si="1"/>
-        <v>54.0281014442443</v>
+        <v>140.946133613586</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>2662</v>
+        <v>13318</v>
       </c>
       <c r="M18" s="1">
         <f t="shared" si="1"/>
-        <v>9482</v>
+        <v>41477</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" si="1"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O18" s="1">
         <f t="shared" si="1"/>
-        <v>198.20635867118801</v>
+        <v>609.92586183547905</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
@@ -2086,23 +2086,23 @@
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <f>MIN(B2:B11)</f>
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" ref="C20:O20" si="2">MIN(C2:C11)</f>
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>0.28563117980956998</v>
+        <v>0.50012660026550204</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
@@ -2114,15 +2114,15 @@
       </c>
       <c r="J20" s="1">
         <f t="shared" si="2"/>
-        <v>7.8276395797729395E-2</v>
+        <v>6.7325592041015597E-2</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="2"/>
-        <v>145</v>
+        <v>411</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" si="2"/>
-        <v>203</v>
+        <v>486</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" si="2"/>
@@ -2130,29 +2130,29 @@
       </c>
       <c r="O20" s="1">
         <f t="shared" si="2"/>
-        <v>0.96251773834228505</v>
+        <v>2.7377154827117902</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <f>MIN(B2:B12)</f>
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" ref="C21:O21" si="3">MIN(C2:C12)</f>
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="3"/>
-        <v>0.28563117980956998</v>
+        <v>0.50012660026550204</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="3"/>
@@ -2164,15 +2164,15 @@
       </c>
       <c r="J21" s="1">
         <f t="shared" si="3"/>
-        <v>7.8276395797729395E-2</v>
+        <v>6.7325592041015597E-2</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" si="3"/>
-        <v>145</v>
+        <v>411</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" si="3"/>
-        <v>203</v>
+        <v>486</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" si="3"/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O21" s="1">
         <f t="shared" si="3"/>
-        <v>0.96251773834228505</v>
+        <v>2.7377154827117902</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
